--- a/saved_data/chartmetric_songstats_dataset_2024_2025.xlsx
+++ b/saved_data/chartmetric_songstats_dataset_2024_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\spotify_music_analysis\saved_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22301CC8-1F0B-4697-8062-E5C62E0EDF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D89937-4B36-4699-AC69-B5ED334D2A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{092EEAB6-AB77-4D44-A4BE-B2376AC2BF93}"/>
   </bookViews>
@@ -694,7 +694,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.08984375" customWidth="1"/>
     <col min="4" max="4" width="4.54296875" customWidth="1"/>
     <col min="5" max="5" width="7.90625" customWidth="1"/>
@@ -788,18 +788,18 @@
         <v>5220000000</v>
       </c>
       <c r="H6">
-        <f>G6/F6</f>
+        <f t="shared" ref="H6:H37" si="0">G6/F6</f>
         <v>4.3499999999999996</v>
       </c>
       <c r="I6">
-        <f>(F6+G6)/E6</f>
+        <f t="shared" ref="I6:I37" si="1">(F6+G6)/E6</f>
         <v>75.618374558303884</v>
       </c>
       <c r="J6" s="2">
         <v>114535770</v>
       </c>
       <c r="K6">
-        <f>E6/J6</f>
+        <f t="shared" ref="K6:K37" si="2">E6/J6</f>
         <v>0.74125314737919867</v>
       </c>
       <c r="L6">
@@ -830,22 +830,22 @@
         <v>406000000</v>
       </c>
       <c r="H7">
-        <f>G7/F7</f>
+        <f t="shared" si="0"/>
         <v>0.80876494023904377</v>
       </c>
       <c r="I7">
-        <f>(F7+G7)/E7</f>
+        <f t="shared" si="1"/>
         <v>17.803921568627452</v>
       </c>
       <c r="J7" s="2">
         <v>114535770</v>
       </c>
       <c r="K7">
-        <f>E7/J7</f>
+        <f t="shared" si="2"/>
         <v>0.44527574224192146</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L61" si="0">((LOG(E7)*0.25)+(LOG(F7)*0.35)+(LOG(G7)*0.25)+((LOG(K7))*0.15))</f>
+        <f t="shared" ref="L7:L61" si="3">((LOG(E7)*0.25)+(LOG(F7)*0.35)+(LOG(G7)*0.25)+((LOG(K7))*0.15))</f>
         <v>7.0715647088578395</v>
       </c>
     </row>
@@ -872,22 +872,22 @@
         <v>294000000</v>
       </c>
       <c r="H8">
-        <f>G8/F8</f>
+        <f t="shared" si="0"/>
         <v>1.0425531914893618</v>
       </c>
       <c r="I8">
-        <f>(F8+G8)/E8</f>
+        <f t="shared" si="1"/>
         <v>43.308270676691727</v>
       </c>
       <c r="J8" s="2">
         <v>114535770</v>
       </c>
       <c r="K8">
-        <f>E8/J8</f>
+        <f t="shared" si="2"/>
         <v>0.11612092885916775</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.7153735059252586</v>
       </c>
     </row>
@@ -914,22 +914,22 @@
         <v>722000000</v>
       </c>
       <c r="H9">
-        <f>G9/F9</f>
+        <f t="shared" si="0"/>
         <v>1.2154882154882154</v>
       </c>
       <c r="I9">
-        <f>(F9+G9)/E9</f>
+        <f t="shared" si="1"/>
         <v>88.322147651006716</v>
       </c>
       <c r="J9" s="2">
         <v>114535770</v>
       </c>
       <c r="K9">
-        <f>E9/J9</f>
+        <f t="shared" si="2"/>
         <v>0.1300903639098947</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.9458928915243456</v>
       </c>
     </row>
@@ -956,22 +956,22 @@
         <v>1640000000</v>
       </c>
       <c r="H10">
-        <f>G10/F10</f>
+        <f t="shared" si="0"/>
         <v>3.4453781512605044</v>
       </c>
       <c r="I10">
-        <f>(F10+G10)/E10</f>
+        <f t="shared" si="1"/>
         <v>34.12903225806452</v>
       </c>
       <c r="J10" s="2">
         <v>114535770</v>
       </c>
       <c r="K10">
-        <f>E10/J10</f>
+        <f t="shared" si="2"/>
         <v>0.54131560821566926</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.2489889002870074</v>
       </c>
     </row>
@@ -998,22 +998,22 @@
         <v>3090000000</v>
       </c>
       <c r="H11">
-        <f>G11/F11</f>
+        <f t="shared" si="0"/>
         <v>4.8508634222919937</v>
       </c>
       <c r="I11">
-        <f>(F11+G11)/E11</f>
+        <f t="shared" si="1"/>
         <v>84.897494305239178</v>
       </c>
       <c r="J11" s="2">
         <v>114535770</v>
       </c>
       <c r="K11">
-        <f>E11/J11</f>
+        <f t="shared" si="2"/>
         <v>0.3832863742043206</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.3020830582940386</v>
       </c>
     </row>
@@ -1040,22 +1040,22 @@
         <v>9380000000</v>
       </c>
       <c r="H12">
-        <f>G12/F12</f>
+        <f t="shared" si="0"/>
         <v>15.52980132450331</v>
       </c>
       <c r="I12">
-        <f>(F12+G12)/E12</f>
+        <f t="shared" si="1"/>
         <v>590.76923076923072</v>
       </c>
       <c r="J12" s="2">
         <v>114535770</v>
       </c>
       <c r="K12">
-        <f>E12/J12</f>
+        <f t="shared" si="2"/>
         <v>0.14755215772330338</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.2487271489812404</v>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
         <v>130000000</v>
       </c>
       <c r="H13">
-        <f>G13/F13</f>
+        <f t="shared" si="0"/>
         <v>0.2927927927927928</v>
       </c>
       <c r="I13">
-        <f>(F13+G13)/E13</f>
+        <f t="shared" si="1"/>
         <v>48.235294117647058</v>
       </c>
       <c r="J13" s="2">
         <v>114535770</v>
       </c>
       <c r="K13">
-        <f>E13/J13</f>
+        <f t="shared" si="2"/>
         <v>0.10389767318978167</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.6764474911974476</v>
       </c>
     </row>
@@ -1124,22 +1124,22 @@
         <v>2060000000</v>
       </c>
       <c r="H14">
-        <f>G14/F14</f>
+        <f t="shared" si="0"/>
         <v>5.6749311294765841</v>
       </c>
       <c r="I14">
-        <f>(F14+G14)/E14</f>
+        <f t="shared" si="1"/>
         <v>52.559652928416483</v>
       </c>
       <c r="J14" s="2">
         <v>114535770</v>
       </c>
       <c r="K14">
-        <f>E14/J14</f>
+        <f t="shared" si="2"/>
         <v>0.4024943473990702</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.1810733230343962</v>
       </c>
     </row>
@@ -1166,22 +1166,22 @@
         <v>607000000</v>
       </c>
       <c r="H15">
-        <f>G15/F15</f>
+        <f t="shared" si="0"/>
         <v>1.9208860759493671</v>
       </c>
       <c r="I15">
-        <f>(F15+G15)/E15</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="J15" s="2">
         <v>114535770</v>
       </c>
       <c r="K15">
-        <f>E15/J15</f>
+        <f t="shared" si="2"/>
         <v>0.12397873607520166</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.8227618184620882</v>
       </c>
     </row>
@@ -1208,22 +1208,22 @@
         <v>2290000000</v>
       </c>
       <c r="H16">
-        <f>G16/F16</f>
+        <f t="shared" si="0"/>
         <v>3.7418300653594772</v>
       </c>
       <c r="I16">
-        <f>(F16+G16)/E16</f>
+        <f t="shared" si="1"/>
         <v>537.40740740740739</v>
       </c>
       <c r="J16" s="2">
         <v>33787910</v>
       </c>
       <c r="K16">
-        <f>E16/J16</f>
+        <f t="shared" si="2"/>
         <v>0.15982048016583447</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.9789651729611641</v>
       </c>
     </row>
@@ -1250,22 +1250,22 @@
         <v>21200000000</v>
       </c>
       <c r="H17">
-        <f>G17/F17</f>
+        <f t="shared" si="0"/>
         <v>31.547619047619047</v>
       </c>
       <c r="I17">
-        <f>(F17+G17)/E17</f>
+        <f t="shared" si="1"/>
         <v>36092.409240924091</v>
       </c>
       <c r="J17" s="2">
         <v>33787910</v>
       </c>
       <c r="K17">
-        <f>E17/J17</f>
+        <f t="shared" si="2"/>
         <v>1.7935409440832533E-2</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.8548380611635995</v>
       </c>
     </row>
@@ -1292,22 +1292,22 @@
         <v>4070000000</v>
       </c>
       <c r="H18">
-        <f>G18/F18</f>
+        <f t="shared" si="0"/>
         <v>5.5753424657534243</v>
       </c>
       <c r="I18">
-        <f>(F18+G18)/E18</f>
+        <f t="shared" si="1"/>
         <v>806.72268907563023</v>
       </c>
       <c r="J18" s="2">
         <v>33787910</v>
       </c>
       <c r="K18">
-        <f>E18/J18</f>
+        <f t="shared" si="2"/>
         <v>0.17609849203457686</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.0850541903359439</v>
       </c>
     </row>
@@ -1334,22 +1334,22 @@
         <v>22500000000</v>
       </c>
       <c r="H19">
-        <f>G19/F19</f>
+        <f t="shared" si="0"/>
         <v>17.307692307692307</v>
       </c>
       <c r="I19">
-        <f>(F19+G19)/E19</f>
+        <f t="shared" si="1"/>
         <v>9834.7107438016537</v>
       </c>
       <c r="J19" s="2">
         <v>33787910</v>
       </c>
       <c r="K19">
-        <f>E19/J19</f>
+        <f t="shared" si="2"/>
         <v>7.1623252222466557E-2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.202137749923466</v>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
         <v>1210000000</v>
       </c>
       <c r="H20">
-        <f>G20/F20</f>
+        <f t="shared" si="0"/>
         <v>2.2365988909426986</v>
       </c>
       <c r="I20">
-        <f>(F20+G20)/E20</f>
+        <f t="shared" si="1"/>
         <v>130.67164179104478</v>
       </c>
       <c r="J20" s="2">
         <v>33787910</v>
       </c>
       <c r="K20">
-        <f>E20/J20</f>
+        <f t="shared" si="2"/>
         <v>0.39659156189299666</v>
       </c>
       <c r="L20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.0488431054083946</v>
       </c>
     </row>
@@ -1418,22 +1418,22 @@
         <v>863000000</v>
       </c>
       <c r="H21">
-        <f>G21/F21</f>
+        <f t="shared" si="0"/>
         <v>1.1078305519897305</v>
       </c>
       <c r="I21">
-        <f>(F21+G21)/E21</f>
+        <f t="shared" si="1"/>
         <v>88.756756756756758</v>
       </c>
       <c r="J21" s="2">
         <v>33787910</v>
       </c>
       <c r="K21">
-        <f>E21/J21</f>
+        <f t="shared" si="2"/>
         <v>0.54753312649406249</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.1235953011714637</v>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
         <v>6080000000</v>
       </c>
       <c r="H22">
-        <f>G22/F22</f>
+        <f t="shared" si="0"/>
         <v>13.362637362637363</v>
       </c>
       <c r="I22">
-        <f>(F22+G22)/E22</f>
+        <f t="shared" si="1"/>
         <v>900.13774104683193</v>
       </c>
       <c r="J22" s="2">
         <v>33787910</v>
       </c>
       <c r="K22">
-        <f>E22/J22</f>
+        <f t="shared" si="2"/>
         <v>0.21486975666739966</v>
       </c>
       <c r="L22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.0913403326242701</v>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>1160000000</v>
       </c>
       <c r="H23">
-        <f>G23/F23</f>
+        <f t="shared" si="0"/>
         <v>2.6363636363636362</v>
       </c>
       <c r="I23">
-        <f>(F23+G23)/E23</f>
+        <f t="shared" si="1"/>
         <v>123.07692307692308</v>
       </c>
       <c r="J23" s="2">
         <v>33787910</v>
       </c>
       <c r="K23">
-        <f>E23/J23</f>
+        <f t="shared" si="2"/>
         <v>0.38475300780663851</v>
       </c>
       <c r="L23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.0075860756956887</v>
       </c>
     </row>
@@ -1544,22 +1544,22 @@
         <v>71900000</v>
       </c>
       <c r="H24">
-        <f>G24/F24</f>
+        <f t="shared" si="0"/>
         <v>1.8871391076115485</v>
       </c>
       <c r="I24">
-        <f>(F24+G24)/E24</f>
+        <f t="shared" si="1"/>
         <v>70.512820512820511</v>
       </c>
       <c r="J24" s="2">
         <v>33787910</v>
       </c>
       <c r="K24">
-        <f>E24/J24</f>
+        <f t="shared" si="2"/>
         <v>4.617036093679662E-2</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.9654416041200307</v>
       </c>
     </row>
@@ -1586,22 +1586,22 @@
         <v>142000000</v>
       </c>
       <c r="H25">
-        <f>G25/F25</f>
+        <f t="shared" si="0"/>
         <v>0.81609195402298851</v>
       </c>
       <c r="I25">
-        <f>(F25+G25)/E25</f>
+        <f t="shared" si="1"/>
         <v>111.26760563380282</v>
       </c>
       <c r="J25" s="2">
         <v>33787910</v>
       </c>
       <c r="K25">
-        <f>E25/J25</f>
+        <f t="shared" si="2"/>
         <v>8.4053734013142575E-2</v>
       </c>
       <c r="L25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.374277459709548</v>
       </c>
     </row>
@@ -1628,22 +1628,22 @@
         <v>1320000000</v>
       </c>
       <c r="H26">
-        <f>G26/F26</f>
+        <f t="shared" si="0"/>
         <v>2.1926910299003324</v>
       </c>
       <c r="I26">
-        <f>(F26+G26)/E26</f>
+        <f t="shared" si="1"/>
         <v>11305.882352941177</v>
       </c>
       <c r="J26" s="2">
         <v>55339000</v>
       </c>
       <c r="K26">
-        <f>E26/J26</f>
+        <f t="shared" si="2"/>
         <v>3.0719745568224942E-3</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.2837271272453981</v>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>8440000</v>
       </c>
       <c r="H27">
-        <f>G27/F27</f>
+        <f t="shared" si="0"/>
         <v>1.1954674220963173</v>
       </c>
       <c r="I27">
-        <f>(F27+G27)/E27</f>
+        <f t="shared" si="1"/>
         <v>233.78582202111613</v>
       </c>
       <c r="J27" s="2">
         <v>55339000</v>
       </c>
       <c r="K27">
-        <f>E27/J27</f>
+        <f t="shared" si="2"/>
         <v>1.1980700771607726E-3</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.8958179723388415</v>
       </c>
     </row>
@@ -1712,22 +1712,22 @@
         <v>335000000</v>
       </c>
       <c r="H28">
-        <f>G28/F28</f>
+        <f t="shared" si="0"/>
         <v>1.8715083798882681</v>
       </c>
       <c r="I28">
-        <f>(F28+G28)/E28</f>
+        <f t="shared" si="1"/>
         <v>161.12852664576803</v>
       </c>
       <c r="J28" s="2">
         <v>55339000</v>
       </c>
       <c r="K28">
-        <f>E28/J28</f>
+        <f t="shared" si="2"/>
         <v>5.7644699036845624E-2</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.4598213397774336</v>
       </c>
     </row>
@@ -1754,22 +1754,22 @@
         <v>53400000</v>
       </c>
       <c r="H29">
-        <f>G29/F29</f>
+        <f t="shared" si="0"/>
         <v>1.2136363636363636</v>
       </c>
       <c r="I29">
-        <f>(F29+G29)/E29</f>
+        <f t="shared" si="1"/>
         <v>24.534005037783377</v>
       </c>
       <c r="J29" s="2">
         <v>55339000</v>
       </c>
       <c r="K29">
-        <f>E29/J29</f>
+        <f t="shared" si="2"/>
         <v>7.1739641121090006E-2</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0851552576849377</v>
       </c>
     </row>
@@ -1796,22 +1796,22 @@
         <v>594000000</v>
       </c>
       <c r="H30">
-        <f>G30/F30</f>
+        <f t="shared" si="0"/>
         <v>4.640625</v>
       </c>
       <c r="I30">
-        <f>(F30+G30)/E30</f>
+        <f t="shared" si="1"/>
         <v>471.89542483660131</v>
       </c>
       <c r="J30" s="2">
         <v>55339000</v>
       </c>
       <c r="K30">
-        <f>E30/J30</f>
+        <f t="shared" si="2"/>
         <v>2.7647771011402447E-2</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.3433919769014793</v>
       </c>
     </row>
@@ -1838,22 +1838,22 @@
         <v>233000000</v>
       </c>
       <c r="H31">
-        <f>G31/F31</f>
+        <f t="shared" si="0"/>
         <v>0.75161290322580643</v>
       </c>
       <c r="I31">
-        <f>(F31+G31)/E31</f>
+        <f t="shared" si="1"/>
         <v>75.626740947075206</v>
       </c>
       <c r="J31" s="2">
         <v>55339000</v>
       </c>
       <c r="K31">
-        <f>E31/J31</f>
+        <f t="shared" si="2"/>
         <v>0.12974574892932653</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.6448106547478067</v>
       </c>
     </row>
@@ -1880,22 +1880,22 @@
         <v>90300000</v>
       </c>
       <c r="H32">
-        <f>G32/F32</f>
+        <f t="shared" si="0"/>
         <v>1.0044493882091212</v>
       </c>
       <c r="I32">
-        <f>(F32+G32)/E32</f>
+        <f t="shared" si="1"/>
         <v>111.92546583850931</v>
       </c>
       <c r="J32" s="2">
         <v>55339000</v>
       </c>
       <c r="K32">
-        <f>E32/J32</f>
+        <f t="shared" si="2"/>
         <v>2.9093406096965972E-2</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0940134840501337</v>
       </c>
     </row>
@@ -1922,22 +1922,22 @@
         <v>379000000</v>
       </c>
       <c r="H33">
-        <f>G33/F33</f>
+        <f t="shared" si="0"/>
         <v>3.2672413793103448</v>
       </c>
       <c r="I33">
-        <f>(F33+G33)/E33</f>
+        <f t="shared" si="1"/>
         <v>174.91166077738515</v>
       </c>
       <c r="J33" s="2">
         <v>55339000</v>
       </c>
       <c r="K33">
-        <f>E33/J33</f>
+        <f t="shared" si="2"/>
         <v>5.1139341151809757E-2</v>
       </c>
       <c r="L33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.3864799768835425</v>
       </c>
     </row>
@@ -1964,22 +1964,22 @@
         <v>1830000</v>
       </c>
       <c r="H34">
-        <f>G34/F34</f>
+        <f t="shared" si="0"/>
         <v>1.4409448818897639</v>
       </c>
       <c r="I34">
-        <f>(F34+G34)/E34</f>
+        <f t="shared" si="1"/>
         <v>60.665362035225051</v>
       </c>
       <c r="J34" s="2">
         <v>55339000</v>
       </c>
       <c r="K34">
-        <f>E34/J34</f>
+        <f t="shared" si="2"/>
         <v>9.2339941090370265E-4</v>
       </c>
       <c r="L34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.4238577387734646</v>
       </c>
     </row>
@@ -2006,22 +2006,22 @@
         <v>267000000</v>
       </c>
       <c r="H35">
-        <f>G35/F35</f>
+        <f t="shared" si="0"/>
         <v>2.2250000000000001</v>
       </c>
       <c r="I35">
-        <f>(F35+G35)/E35</f>
+        <f t="shared" si="1"/>
         <v>184.28571428571428</v>
       </c>
       <c r="J35" s="2">
         <v>55339000</v>
       </c>
       <c r="K35">
-        <f>E35/J35</f>
+        <f t="shared" si="2"/>
         <v>3.7947920996042571E-2</v>
       </c>
       <c r="L35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.301774273303768</v>
       </c>
     </row>
@@ -2048,22 +2048,22 @@
         <v>17600000000</v>
       </c>
       <c r="H36">
-        <f>G36/F36</f>
+        <f t="shared" si="0"/>
         <v>1.4789915966386555</v>
       </c>
       <c r="I36">
-        <f>(F36+G36)/E36</f>
+        <f t="shared" si="1"/>
         <v>573.92996108949421</v>
       </c>
       <c r="J36" s="2">
         <v>227882950</v>
       </c>
       <c r="K36">
-        <f>E36/J36</f>
+        <f t="shared" si="2"/>
         <v>0.22555439097132979</v>
       </c>
       <c r="L36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.9185480761087845</v>
       </c>
     </row>
@@ -2090,22 +2090,22 @@
         <v>21200000000</v>
       </c>
       <c r="H37">
-        <f>G37/F37</f>
+        <f t="shared" si="0"/>
         <v>1.696</v>
       </c>
       <c r="I37">
-        <f>(F37+G37)/E37</f>
+        <f t="shared" si="1"/>
         <v>546.19124797406812</v>
       </c>
       <c r="J37" s="2">
         <v>227882950</v>
       </c>
       <c r="K37">
-        <f>E37/J37</f>
+        <f t="shared" si="2"/>
         <v>0.27075303352005931</v>
       </c>
       <c r="L37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.977959760468055</v>
       </c>
     </row>
@@ -2132,22 +2132,22 @@
         <v>255000000000</v>
       </c>
       <c r="H38">
-        <f>G38/F38</f>
+        <f t="shared" ref="H38:H69" si="4">G38/F38</f>
         <v>31.914893617021278</v>
       </c>
       <c r="I38">
-        <f>(F38+G38)/E38</f>
+        <f t="shared" ref="I38:I61" si="5">(F38+G38)/E38</f>
         <v>9740.3703703703704</v>
       </c>
       <c r="J38" s="2">
         <v>227882950</v>
       </c>
       <c r="K38">
-        <f>E38/J38</f>
+        <f t="shared" ref="K38:K69" si="6">E38/J38</f>
         <v>0.11848187852579581</v>
       </c>
       <c r="L38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.0364151486017334</v>
       </c>
     </row>
@@ -2174,22 +2174,22 @@
         <v>13400000000</v>
       </c>
       <c r="H39">
-        <f>G39/F39</f>
+        <f t="shared" si="4"/>
         <v>3.6314363143631438</v>
       </c>
       <c r="I39">
-        <f>(F39+G39)/E39</f>
+        <f t="shared" si="5"/>
         <v>769.81981981981983</v>
       </c>
       <c r="J39" s="2">
         <v>227882950</v>
       </c>
       <c r="K39">
-        <f>E39/J39</f>
+        <f t="shared" si="6"/>
         <v>9.7418433454543221E-2</v>
       </c>
       <c r="L39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.5651198425968795</v>
       </c>
     </row>
@@ -2216,22 +2216,22 @@
         <v>18400000000</v>
       </c>
       <c r="H40">
-        <f>G40/F40</f>
+        <f t="shared" si="4"/>
         <v>3.1186440677966103</v>
       </c>
       <c r="I40">
-        <f>(F40+G40)/E40</f>
+        <f t="shared" si="5"/>
         <v>409.78077571669479</v>
       </c>
       <c r="J40" s="2">
         <v>227882950</v>
       </c>
       <c r="K40">
-        <f>E40/J40</f>
+        <f t="shared" si="6"/>
         <v>0.26022131098443302</v>
       </c>
       <c r="L40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.8415677622425921</v>
       </c>
     </row>
@@ -2258,22 +2258,22 @@
         <v>9250000000</v>
       </c>
       <c r="H41">
-        <f>G41/F41</f>
+        <f t="shared" si="4"/>
         <v>2.9179810725552051</v>
       </c>
       <c r="I41">
-        <f>(F41+G41)/E41</f>
+        <f t="shared" si="5"/>
         <v>730.58823529411768</v>
       </c>
       <c r="J41" s="2">
         <v>227882950</v>
       </c>
       <c r="K41">
-        <f>E41/J41</f>
+        <f t="shared" si="6"/>
         <v>7.4599701294019577E-2</v>
       </c>
       <c r="L41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.4554289685820319</v>
       </c>
     </row>
@@ -2300,22 +2300,22 @@
         <v>13000000000</v>
       </c>
       <c r="H42">
-        <f>G42/F42</f>
+        <f t="shared" si="4"/>
         <v>2.4809160305343512</v>
       </c>
       <c r="I42">
-        <f>(F42+G42)/E42</f>
+        <f t="shared" si="5"/>
         <v>1361.1940298507463</v>
       </c>
       <c r="J42" s="2">
         <v>227882950</v>
       </c>
       <c r="K42">
-        <f>E42/J42</f>
+        <f t="shared" si="6"/>
         <v>5.880211749058014E-2</v>
       </c>
       <c r="L42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.5274369329366877</v>
       </c>
     </row>
@@ -2342,22 +2342,22 @@
         <v>5650000000</v>
       </c>
       <c r="H43">
-        <f>G43/F43</f>
+        <f t="shared" si="4"/>
         <v>1.7711598746081505</v>
       </c>
       <c r="I43">
-        <f>(F43+G43)/E43</f>
+        <f t="shared" si="5"/>
         <v>442</v>
       </c>
       <c r="J43" s="2">
         <v>227882950</v>
       </c>
       <c r="K43">
-        <f>E43/J43</f>
+        <f t="shared" si="6"/>
         <v>8.7764354463552449E-2</v>
       </c>
       <c r="L43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.4310940743602165</v>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>9370000000</v>
       </c>
       <c r="H44">
-        <f>G44/F44</f>
+        <f t="shared" si="4"/>
         <v>3.287719298245614</v>
       </c>
       <c r="I44">
-        <f>(F44+G44)/E44</f>
+        <f t="shared" si="5"/>
         <v>985.48387096774195</v>
       </c>
       <c r="J44" s="2">
         <v>227882950</v>
       </c>
       <c r="K44">
-        <f>E44/J44</f>
+        <f t="shared" si="6"/>
         <v>5.4413899767402518E-2</v>
       </c>
       <c r="L44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.385842497859568</v>
       </c>
     </row>
@@ -2426,22 +2426,22 @@
         <v>14900000000</v>
       </c>
       <c r="H45">
-        <f>G45/F45</f>
+        <f t="shared" si="4"/>
         <v>5.6870229007633588</v>
       </c>
       <c r="I45">
-        <f>(F45+G45)/E45</f>
+        <f t="shared" si="5"/>
         <v>663.63636363636363</v>
       </c>
       <c r="J45" s="2">
         <v>227882950</v>
       </c>
       <c r="K45">
-        <f>E45/J45</f>
+        <f t="shared" si="6"/>
         <v>0.11584894789188924</v>
       </c>
       <c r="L45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.5546868148826629</v>
       </c>
     </row>
@@ -2468,22 +2468,22 @@
         <v>61600000000</v>
       </c>
       <c r="H46">
-        <f>G46/F46</f>
+        <f t="shared" si="4"/>
         <v>22.985074626865671</v>
       </c>
       <c r="I46">
-        <f>(F46+G46)/E46</f>
+        <f t="shared" si="5"/>
         <v>2472.3076923076924</v>
       </c>
       <c r="J46" s="2">
         <v>63212380</v>
       </c>
       <c r="K46">
-        <f>E46/J46</f>
+        <f t="shared" si="6"/>
         <v>0.41131183480198025</v>
       </c>
       <c r="L46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.7931113738105449</v>
       </c>
     </row>
@@ -2510,22 +2510,22 @@
         <v>404000000</v>
       </c>
       <c r="H47">
-        <f>G47/F47</f>
+        <f t="shared" si="4"/>
         <v>2.5897435897435899</v>
       </c>
       <c r="I47">
-        <f>(F47+G47)/E47</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="J47" s="2">
         <v>63212380</v>
       </c>
       <c r="K47">
-        <f>E47/J47</f>
+        <f t="shared" si="6"/>
         <v>1.7718048268392995E-2</v>
       </c>
       <c r="L47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.2687558384408195</v>
       </c>
     </row>
@@ -2552,22 +2552,22 @@
         <v>4950000000</v>
       </c>
       <c r="H48">
-        <f>G48/F48</f>
+        <f t="shared" si="4"/>
         <v>2.4264705882352939</v>
       </c>
       <c r="I48">
-        <f>(F48+G48)/E48</f>
+        <f t="shared" si="5"/>
         <v>1044.8430493273543</v>
       </c>
       <c r="J48" s="2">
         <v>63212380</v>
       </c>
       <c r="K48">
-        <f>E48/J48</f>
+        <f t="shared" si="6"/>
         <v>0.10583369903174031</v>
       </c>
       <c r="L48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.2420719841106207</v>
       </c>
     </row>
@@ -2594,22 +2594,22 @@
         <v>798000000</v>
       </c>
       <c r="H49">
-        <f>G49/F49</f>
+        <f t="shared" si="4"/>
         <v>3.3670886075949369</v>
       </c>
       <c r="I49">
-        <f>(F49+G49)/E49</f>
+        <f t="shared" si="5"/>
         <v>841.46341463414637</v>
       </c>
       <c r="J49" s="2">
         <v>63212380</v>
       </c>
       <c r="K49">
-        <f>E49/J49</f>
+        <f t="shared" si="6"/>
         <v>1.9458213723324451E-2</v>
       </c>
       <c r="L49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.4225043671880124</v>
       </c>
     </row>
@@ -2636,22 +2636,22 @@
         <v>2660000000</v>
       </c>
       <c r="H50">
-        <f>G50/F50</f>
+        <f t="shared" si="4"/>
         <v>1.4</v>
       </c>
       <c r="I50">
-        <f>(F50+G50)/E50</f>
+        <f t="shared" si="5"/>
         <v>340.29850746268659</v>
       </c>
       <c r="J50" s="2">
         <v>63212380</v>
       </c>
       <c r="K50">
-        <f>E50/J50</f>
+        <f t="shared" si="6"/>
         <v>0.21198379178255905</v>
       </c>
       <c r="L50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.2845057675082137</v>
       </c>
     </row>
@@ -2678,22 +2678,22 @@
         <v>205000000</v>
       </c>
       <c r="H51">
-        <f>G51/F51</f>
+        <f t="shared" si="4"/>
         <v>1.6141732283464567</v>
       </c>
       <c r="I51">
-        <f>(F51+G51)/E51</f>
+        <f t="shared" si="5"/>
         <v>1580.952380952381</v>
       </c>
       <c r="J51" s="2">
         <v>63212380</v>
       </c>
       <c r="K51">
-        <f>E51/J51</f>
+        <f t="shared" si="6"/>
         <v>3.3221340503236866E-3</v>
       </c>
       <c r="L51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.8730371641631258</v>
       </c>
     </row>
@@ -2720,22 +2720,22 @@
         <v>1750000000</v>
       </c>
       <c r="H52">
-        <f>G52/F52</f>
+        <f t="shared" si="4"/>
         <v>8.064516129032258</v>
       </c>
       <c r="I52">
-        <f>(F52+G52)/E52</f>
+        <f t="shared" si="5"/>
         <v>19475.247524752474</v>
       </c>
       <c r="J52" s="2">
         <v>63212380</v>
       </c>
       <c r="K52">
-        <f>E52/J52</f>
+        <f t="shared" si="6"/>
         <v>1.597788281346154E-3</v>
       </c>
       <c r="L52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0601286472026494</v>
       </c>
     </row>
@@ -2762,22 +2762,22 @@
         <v>16200000000</v>
       </c>
       <c r="H53">
-        <f>G53/F53</f>
+        <f t="shared" si="4"/>
         <v>14.086956521739131</v>
       </c>
       <c r="I53">
-        <f>(F53+G53)/E53</f>
+        <f t="shared" si="5"/>
         <v>3476.9539078156313</v>
       </c>
       <c r="J53" s="2">
         <v>63212380</v>
       </c>
       <c r="K53">
-        <f>E53/J53</f>
+        <f t="shared" si="6"/>
         <v>7.8940232910072364E-2</v>
       </c>
       <c r="L53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.2327428946798129</v>
       </c>
     </row>
@@ -2804,22 +2804,22 @@
         <v>1400000000</v>
       </c>
       <c r="H54">
-        <f>G54/F54</f>
+        <f t="shared" si="4"/>
         <v>3.3096926713947989</v>
       </c>
       <c r="I54">
-        <f>(F54+G54)/E54</f>
+        <f t="shared" si="5"/>
         <v>617.96610169491521</v>
       </c>
       <c r="J54" s="2">
         <v>63212380</v>
       </c>
       <c r="K54">
-        <f>E54/J54</f>
+        <f t="shared" si="6"/>
         <v>4.6668073564070836E-2</v>
       </c>
       <c r="L54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.7235596225631244</v>
       </c>
     </row>
@@ -2846,22 +2846,22 @@
         <v>208000000</v>
       </c>
       <c r="H55">
-        <f>G55/F55</f>
+        <f t="shared" si="4"/>
         <v>1.3594771241830066</v>
       </c>
       <c r="I55">
-        <f>(F55+G55)/E55</f>
+        <f t="shared" si="5"/>
         <v>612.90322580645159</v>
       </c>
       <c r="J55" s="2">
         <v>63212380</v>
       </c>
       <c r="K55">
-        <f>E55/J55</f>
+        <f t="shared" si="6"/>
         <v>9.3177950268602452E-3</v>
       </c>
       <c r="L55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0820836311127247</v>
       </c>
     </row>
@@ -2888,22 +2888,22 @@
         <v>317000000000</v>
       </c>
       <c r="H56">
-        <f>G56/F56</f>
+        <f t="shared" si="4"/>
         <v>4.0382165605095546</v>
       </c>
       <c r="I56">
-        <f>(F56+G56)/E56</f>
+        <f t="shared" si="5"/>
         <v>1363.7931034482758</v>
       </c>
       <c r="J56" s="2">
         <v>334914900</v>
       </c>
       <c r="K56">
-        <f>E56/J56</f>
+        <f t="shared" si="6"/>
         <v>0.8658916041059983</v>
       </c>
       <c r="L56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.7946882241859647</v>
       </c>
     </row>
@@ -2930,22 +2930,22 @@
         <v>344000000000</v>
       </c>
       <c r="H57">
-        <f>G57/F57</f>
+        <f t="shared" si="4"/>
         <v>3.7760702524698133</v>
       </c>
       <c r="I57">
-        <f>(F57+G57)/E57</f>
+        <f t="shared" si="5"/>
         <v>1347.0588235294117</v>
       </c>
       <c r="J57" s="2">
         <v>68350000</v>
       </c>
       <c r="K57">
-        <f>E57/J57</f>
+        <f t="shared" si="6"/>
         <v>4.7256766642282368</v>
       </c>
       <c r="L57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.948441273680297</v>
       </c>
     </row>
@@ -2972,22 +2972,22 @@
         <v>150000000000</v>
       </c>
       <c r="H58">
-        <f>G58/F58</f>
+        <f t="shared" si="4"/>
         <v>2.2935779816513762</v>
       </c>
       <c r="I58">
-        <f>(F58+G58)/E58</f>
+        <f t="shared" si="5"/>
         <v>1252.3255813953488</v>
       </c>
       <c r="J58" s="2">
         <v>68287490</v>
       </c>
       <c r="K58">
-        <f>E58/J58</f>
+        <f t="shared" si="6"/>
         <v>2.5187629535072968</v>
       </c>
       <c r="L58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.6985352329517305</v>
       </c>
     </row>
@@ -3014,22 +3014,22 @@
         <v>283000000000</v>
       </c>
       <c r="H59">
-        <f>G59/F59</f>
+        <f t="shared" si="4"/>
         <v>14.663212435233161</v>
       </c>
       <c r="I59">
-        <f>(F59+G59)/E59</f>
+        <f t="shared" si="5"/>
         <v>22729.323308270676</v>
       </c>
       <c r="J59" s="2">
         <v>83280000</v>
       </c>
       <c r="K59">
-        <f>E59/J59</f>
+        <f t="shared" si="6"/>
         <v>0.15970220941402496</v>
       </c>
       <c r="L59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.1243512159452553</v>
       </c>
     </row>
@@ -3056,22 +3056,22 @@
         <v>210000000000</v>
       </c>
       <c r="H60">
-        <f>G60/F60</f>
+        <f t="shared" si="4"/>
         <v>1.7647058823529411</v>
       </c>
       <c r="I60">
-        <f>(F60+G60)/E60</f>
+        <f t="shared" si="5"/>
         <v>1085.8085808580859</v>
       </c>
       <c r="J60" s="2">
         <v>40097760</v>
       </c>
       <c r="K60">
-        <f>E60/J60</f>
+        <f t="shared" si="6"/>
         <v>7.5565318361923461</v>
       </c>
       <c r="L60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.9591052947566077</v>
       </c>
     </row>
@@ -3098,22 +3098,22 @@
         <v>117000000000</v>
       </c>
       <c r="H61">
-        <f>G61/F61</f>
+        <f t="shared" si="4"/>
         <v>11.842105263157896</v>
       </c>
       <c r="I61">
-        <f>(F61+G61)/E61</f>
+        <f t="shared" si="5"/>
         <v>4229.333333333333</v>
       </c>
       <c r="J61" s="2">
         <v>58993470</v>
       </c>
       <c r="K61">
-        <f>E61/J61</f>
+        <f t="shared" si="6"/>
         <v>0.50853085943240839</v>
       </c>
       <c r="L61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.0904393066072711</v>
       </c>
     </row>
